--- a/data/trans_orig/P1416-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1416-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de alergias crónicas en 2007</t>
+          <t>Población con diagnóstico de alergias crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29993</t>
+          <t>28737</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53595</t>
+          <t>53377</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39364</t>
+          <t>41265</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67504</t>
+          <t>67647</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75962</t>
+          <t>78425</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114605</t>
+          <t>112074</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>440469</t>
+          <t>440687</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>464071</t>
+          <t>465327</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>399985</t>
+          <t>399842</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>428125</t>
+          <t>426224</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>846948</t>
+          <t>849479</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>885591</t>
+          <t>883128</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46497</t>
+          <t>45545</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77033</t>
+          <t>78128</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53299</t>
+          <t>51693</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84504</t>
+          <t>85430</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>103178</t>
+          <t>108752</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>148631</t>
+          <t>151225</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>658456</t>
+          <t>657361</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>688992</t>
+          <t>689944</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>540990</t>
+          <t>540064</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>572195</t>
+          <t>573801</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1212351</t>
+          <t>1209757</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1257804</t>
+          <t>1252230</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30615</t>
+          <t>31690</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56953</t>
+          <t>57503</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59014</t>
+          <t>59590</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91431</t>
+          <t>92784</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>99788</t>
+          <t>97063</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141679</t>
+          <t>141254</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>581715</t>
+          <t>581165</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>608053</t>
+          <t>606978</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>598313</t>
+          <t>596960</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>630730</t>
+          <t>630154</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1186733</t>
+          <t>1187158</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1228624</t>
+          <t>1231349</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17944</t>
+          <t>18339</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>39747</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38580</t>
+          <t>38335</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66526</t>
+          <t>67362</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62988</t>
+          <t>61284</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98970</t>
+          <t>99497</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>478341</t>
+          <t>479400</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>501203</t>
+          <t>500808</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>449116</t>
+          <t>448280</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>477062</t>
+          <t>477307</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>935819</t>
+          <t>935292</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>971801</t>
+          <t>973505</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16933</t>
+          <t>16898</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37317</t>
+          <t>36415</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19654</t>
+          <t>19988</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40731</t>
+          <t>41913</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39878</t>
+          <t>40720</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69436</t>
+          <t>69990</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>349393</t>
+          <t>350295</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>369777</t>
+          <t>369812</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>363255</t>
+          <t>362073</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>384332</t>
+          <t>383998</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>721260</t>
+          <t>720706</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>750818</t>
+          <t>749976</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7802</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22178</t>
+          <t>23149</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24113</t>
+          <t>24401</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45717</t>
+          <t>45809</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35313</t>
+          <t>35801</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61752</t>
+          <t>62049</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>270405</t>
+          <t>269434</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>284781</t>
+          <t>284517</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>297217</t>
+          <t>297125</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>318821</t>
+          <t>318533</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>573765</t>
+          <t>573468</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>600204</t>
+          <t>599716</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15686</t>
+          <t>15978</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>8639</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24786</t>
+          <t>24653</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15367</t>
+          <t>14820</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36419</t>
+          <t>36724</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>194197</t>
+          <t>193905</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>205499</t>
+          <t>205861</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>309122</t>
+          <t>309255</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>325296</t>
+          <t>325269</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>507372</t>
+          <t>507067</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>528424</t>
+          <t>528971</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>194709</t>
+          <t>193186</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>253999</t>
+          <t>249909</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>289998</t>
+          <t>290318</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>360635</t>
+          <t>357888</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>498737</t>
+          <t>501629</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>587273</t>
+          <t>590728</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3022544</t>
+          <t>3026634</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3081834</t>
+          <t>3083357</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3018562</t>
+          <t>3021309</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3089199</t>
+          <t>3088879</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6068468</t>
+          <t>6065013</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6157004</t>
+          <t>6154112</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de alergias crónicas en 2012</t>
+          <t>Población con diagnóstico de alergias crónicas en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27273</t>
+          <t>28358</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51751</t>
+          <t>51343</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28966</t>
+          <t>27698</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53553</t>
+          <t>52160</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61559</t>
+          <t>62038</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93107</t>
+          <t>94815</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>402395</t>
+          <t>402803</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>426873</t>
+          <t>425788</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>376677</t>
+          <t>378070</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>401264</t>
+          <t>402532</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>791269</t>
+          <t>789561</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>822817</t>
+          <t>822338</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,99%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33837</t>
+          <t>33226</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58729</t>
+          <t>59911</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38462</t>
+          <t>39249</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66332</t>
+          <t>67108</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77100</t>
+          <t>78658</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115431</t>
+          <t>114736</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>628358</t>
+          <t>627176</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>653250</t>
+          <t>653861</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>543923</t>
+          <t>543147</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>571793</t>
+          <t>571006</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1181911</t>
+          <t>1182606</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1220242</t>
+          <t>1218684</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30524</t>
+          <t>29473</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57465</t>
+          <t>57195</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60131</t>
+          <t>60383</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95529</t>
+          <t>95780</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>99549</t>
+          <t>97968</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141901</t>
+          <t>141613</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>623376</t>
+          <t>623646</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>650317</t>
+          <t>651368</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>614045</t>
+          <t>613794</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>649443</t>
+          <t>649191</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1248514</t>
+          <t>1248802</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1290866</t>
+          <t>1292447</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>8406</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24593</t>
+          <t>26264</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26273</t>
+          <t>26900</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53475</t>
+          <t>53277</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38640</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69648</t>
+          <t>69338</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>590024</t>
+          <t>588353</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>606928</t>
+          <t>606211</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>562724</t>
+          <t>562922</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>589926</t>
+          <t>589299</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1161168</t>
+          <t>1161478</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1192176</t>
+          <t>1191930</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24063</t>
+          <t>23753</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11503</t>
+          <t>12319</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29987</t>
+          <t>30385</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24050</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46908</t>
+          <t>48230</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>405366</t>
+          <t>405676</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>420913</t>
+          <t>421009</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>417813</t>
+          <t>417415</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>436297</t>
+          <t>435481</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>830321</t>
+          <t>828999</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>853179</t>
+          <t>852892</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>6220</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23731</t>
+          <t>22305</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>8858</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23910</t>
+          <t>24059</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17574</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38680</t>
+          <t>39219</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>286055</t>
+          <t>287481</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>303536</t>
+          <t>303566</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>330086</t>
+          <t>329937</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>345210</t>
+          <t>345138</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>625102</t>
+          <t>624563</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>646208</t>
+          <t>645413</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16585</t>
+          <t>18396</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>13213</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32888</t>
+          <t>31936</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20157</t>
+          <t>19795</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42827</t>
+          <t>42058</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>233266</t>
+          <t>231455</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>246601</t>
+          <t>245734</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>356091</t>
+          <t>357043</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>375777</t>
+          <t>375766</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>596003</t>
+          <t>596772</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>618673</t>
+          <t>619035</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>152076</t>
+          <t>150737</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>206038</t>
+          <t>203071</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>229317</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>293579</t>
+          <t>293884</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>397343</t>
+          <t>398486</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>480849</t>
+          <t>481127</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3219719</t>
+          <t>3222686</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3273681</t>
+          <t>3275020</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3263455</t>
+          <t>3263150</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3332095</t>
+          <t>3327717</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6501941</t>
+          <t>6501663</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6585447</t>
+          <t>6584304</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de alergias crónicas en 2016</t>
+          <t>Población con diagnóstico de alergias crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31705</t>
+          <t>31791</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56039</t>
+          <t>58384</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27702</t>
+          <t>26567</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50443</t>
+          <t>49931</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65587</t>
+          <t>65862</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101516</t>
+          <t>97817</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>363424</t>
+          <t>361079</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>387758</t>
+          <t>387672</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>345312</t>
+          <t>345824</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>368053</t>
+          <t>369188</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>713702</t>
+          <t>717401</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>749631</t>
+          <t>749356</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,92%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28463</t>
+          <t>26344</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52653</t>
+          <t>50306</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41719</t>
+          <t>41913</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69692</t>
+          <t>68911</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76359</t>
+          <t>75406</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113504</t>
+          <t>112078</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>537843</t>
+          <t>540190</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>562033</t>
+          <t>564152</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>493852</t>
+          <t>494633</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>521825</t>
+          <t>521631</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1040536</t>
+          <t>1041962</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1077681</t>
+          <t>1078634</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22267</t>
+          <t>22760</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45127</t>
+          <t>45852</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51990</t>
+          <t>51521</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83634</t>
+          <t>82386</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79889</t>
+          <t>81030</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119113</t>
+          <t>119527</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>623970</t>
+          <t>623245</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>646830</t>
+          <t>646337</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>577752</t>
+          <t>579000</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>609396</t>
+          <t>609865</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1211370</t>
+          <t>1210956</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1250594</t>
+          <t>1249453</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14129</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33537</t>
+          <t>32773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37121</t>
+          <t>38209</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66405</t>
+          <t>65312</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56683</t>
+          <t>56040</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90266</t>
+          <t>89811</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>612511</t>
+          <t>613275</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>631919</t>
+          <t>631918</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>582672</t>
+          <t>583765</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>611956</t>
+          <t>610868</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1204859</t>
+          <t>1205314</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1238442</t>
+          <t>1239085</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29348</t>
+          <t>29855</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28596</t>
+          <t>28820</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54550</t>
+          <t>54199</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44942</t>
+          <t>44605</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76299</t>
+          <t>76316</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>448570</t>
+          <t>448063</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>466352</t>
+          <t>466497</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>442299</t>
+          <t>442650</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>468253</t>
+          <t>468029</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>898468</t>
+          <t>898451</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>929825</t>
+          <t>930162</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10509</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22127</t>
+          <t>21799</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11098</t>
+          <t>10873</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27488</t>
+          <t>27786</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>324023</t>
+          <t>323821</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332504</t>
+          <t>332486</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>355635</t>
+          <t>355963</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>370264</t>
+          <t>369758</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>684604</t>
+          <t>684306</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>700994</t>
+          <t>701219</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15248</t>
+          <t>14881</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11405</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31637</t>
+          <t>31768</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18240</t>
+          <t>18814</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40603</t>
+          <t>40684</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>241750</t>
+          <t>242117</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>252846</t>
+          <t>252826</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>368532</t>
+          <t>368401</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>388764</t>
+          <t>387764</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>616564</t>
+          <t>616483</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>638927</t>
+          <t>638353</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>144483</t>
+          <t>142682</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>194920</t>
+          <t>196124</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>250666</t>
+          <t>242891</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>316062</t>
+          <t>311813</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>410259</t>
+          <t>409329</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>499273</t>
+          <t>495829</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3199430</t>
+          <t>3198226</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3249867</t>
+          <t>3251668</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3228480</t>
+          <t>3232729</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3293876</t>
+          <t>3301651</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6439619</t>
+          <t>6443063</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6528633</t>
+          <t>6529563</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de alergias crónicas en 2023</t>
+          <t>Población con diagnóstico de alergias crónicas en 2023 (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41983</t>
+          <t>44157</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95100</t>
+          <t>98280</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20413</t>
+          <t>19608</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49984</t>
+          <t>47877</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71771</t>
+          <t>70809</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133696</t>
+          <t>132568</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>304887</t>
+          <t>301707</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>358004</t>
+          <t>355830</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>260865</t>
+          <t>262972</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>290436</t>
+          <t>291241</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>577140</t>
+          <t>578268</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>639065</t>
+          <t>640027</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,04%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33872</t>
+          <t>33809</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69436</t>
+          <t>67319</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37725</t>
+          <t>36696</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78821</t>
+          <t>78295</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79259</t>
+          <t>81938</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>134935</t>
+          <t>134816</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>354111</t>
+          <t>356228</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>389675</t>
+          <t>389738</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>426850</t>
+          <t>427376</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>467946</t>
+          <t>468975</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>794283</t>
+          <t>794402</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>849959</t>
+          <t>847280</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,18%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47529</t>
+          <t>48989</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82526</t>
+          <t>78562</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50466</t>
+          <t>50649</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74822</t>
+          <t>73655</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105351</t>
+          <t>105344</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>143549</t>
+          <t>143352</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>453812</t>
+          <t>457776</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>488809</t>
+          <t>487349</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>466238</t>
+          <t>467405</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>490594</t>
+          <t>490411</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>933850</t>
+          <t>934047</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>972048</t>
+          <t>972055</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29214</t>
+          <t>28107</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102354</t>
+          <t>102144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80965</t>
+          <t>82498</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116483</t>
+          <t>117127</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106154</t>
+          <t>99724</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>206021</t>
+          <t>206775</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>782452</t>
+          <t>782662</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>855592</t>
+          <t>856699</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>593881</t>
+          <t>593237</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>629399</t>
+          <t>627866</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1389150</t>
+          <t>1388396</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1489017</t>
+          <t>1495447</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33522</t>
+          <t>32876</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56084</t>
+          <t>56562</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54975</t>
+          <t>54630</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77375</t>
+          <t>77185</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93737</t>
+          <t>93283</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>126617</t>
+          <t>126919</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>503195</t>
+          <t>502717</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>525757</t>
+          <t>526403</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>465160</t>
+          <t>465350</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>487560</t>
+          <t>487905</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>975197</t>
+          <t>974895</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1008077</t>
+          <t>1008531</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14246</t>
+          <t>13856</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28670</t>
+          <t>28431</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14441</t>
+          <t>16650</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63775</t>
+          <t>63329</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28859</t>
+          <t>32195</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80751</t>
+          <t>81369</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>338777</t>
+          <t>339016</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>353201</t>
+          <t>353591</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>544048</t>
+          <t>544494</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>593382</t>
+          <t>591173</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>894519</t>
+          <t>893901</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>946411</t>
+          <t>943075</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>10231</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21463</t>
+          <t>21367</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27364</t>
+          <t>27509</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44813</t>
+          <t>44361</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41513</t>
+          <t>40596</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60858</t>
+          <t>61930</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>261296</t>
+          <t>261392</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>272774</t>
+          <t>272528</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>380717</t>
+          <t>381169</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>398166</t>
+          <t>398021</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>647431</t>
+          <t>646359</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>666776</t>
+          <t>667693</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>251169</t>
+          <t>255310</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>374599</t>
+          <t>379206</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>313196</t>
+          <t>320292</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>434456</t>
+          <t>440376</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>626449</t>
+          <t>623311</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>791239</t>
+          <t>790962</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3079565</t>
+          <t>3074958</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3202995</t>
+          <t>3198854</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3209376</t>
+          <t>3203456</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3330636</t>
+          <t>3323540</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6306757</t>
+          <t>6307034</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6471547</t>
+          <t>6474685</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1416-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1416-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28737</t>
+          <t>30263</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53377</t>
+          <t>53765</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41265</t>
+          <t>41058</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67647</t>
+          <t>67362</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78425</t>
+          <t>74524</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112074</t>
+          <t>109951</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>440687</t>
+          <t>440299</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>465327</t>
+          <t>463801</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>399842</t>
+          <t>400127</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>426224</t>
+          <t>426431</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>849479</t>
+          <t>851602</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>883128</t>
+          <t>887029</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>92,25%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45545</t>
+          <t>46957</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78128</t>
+          <t>77490</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51693</t>
+          <t>51584</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85430</t>
+          <t>83542</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108752</t>
+          <t>106354</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>151225</t>
+          <t>150411</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>657361</t>
+          <t>657999</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>689944</t>
+          <t>688532</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>540064</t>
+          <t>541952</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>573801</t>
+          <t>573910</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1209757</t>
+          <t>1210571</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1252230</t>
+          <t>1254628</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,19%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31690</t>
+          <t>29292</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57503</t>
+          <t>55831</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59590</t>
+          <t>58810</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92784</t>
+          <t>91983</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97063</t>
+          <t>96747</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141254</t>
+          <t>139681</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>581165</t>
+          <t>582837</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>606978</t>
+          <t>609376</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>596960</t>
+          <t>597761</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>630154</t>
+          <t>630934</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1187158</t>
+          <t>1188731</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1231349</t>
+          <t>1231665</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18339</t>
+          <t>18104</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39747</t>
+          <t>41902</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38335</t>
+          <t>38279</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67362</t>
+          <t>64409</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61284</t>
+          <t>63131</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99497</t>
+          <t>98310</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>479400</t>
+          <t>477245</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>500808</t>
+          <t>501043</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>448280</t>
+          <t>451233</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>477307</t>
+          <t>477363</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>935292</t>
+          <t>936479</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>973505</t>
+          <t>971658</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16898</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36415</t>
+          <t>35873</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19988</t>
+          <t>19554</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41913</t>
+          <t>41580</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40720</t>
+          <t>41393</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69990</t>
+          <t>69820</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>350295</t>
+          <t>350837</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>369812</t>
+          <t>370454</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>362073</t>
+          <t>362406</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>383998</t>
+          <t>384432</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>720706</t>
+          <t>720876</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>749976</t>
+          <t>749303</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23149</t>
+          <t>22435</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24401</t>
+          <t>24725</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45809</t>
+          <t>46189</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35801</t>
+          <t>35349</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62049</t>
+          <t>61238</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>269434</t>
+          <t>270148</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>284517</t>
+          <t>285294</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>297125</t>
+          <t>296745</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>318533</t>
+          <t>318209</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>573468</t>
+          <t>574279</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>599716</t>
+          <t>600168</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>4460</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15978</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8639</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24653</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14820</t>
+          <t>14041</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36724</t>
+          <t>35035</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>193905</t>
+          <t>194092</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>205861</t>
+          <t>205423</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>309255</t>
+          <t>308914</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>325269</t>
+          <t>325516</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>507067</t>
+          <t>508756</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>528971</t>
+          <t>529750</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>193186</t>
+          <t>188622</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>249909</t>
+          <t>250643</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>290318</t>
+          <t>291854</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>357888</t>
+          <t>358099</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>501629</t>
+          <t>499853</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>590728</t>
+          <t>593898</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3026634</t>
+          <t>3025900</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3083357</t>
+          <t>3087921</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3021309</t>
+          <t>3021098</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3088879</t>
+          <t>3087343</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6065013</t>
+          <t>6061843</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6154112</t>
+          <t>6155888</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28358</t>
+          <t>27882</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51343</t>
+          <t>53409</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27698</t>
+          <t>28001</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52160</t>
+          <t>51104</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62038</t>
+          <t>61640</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94815</t>
+          <t>95628</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>402803</t>
+          <t>400737</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425788</t>
+          <t>426264</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>378070</t>
+          <t>379126</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>402532</t>
+          <t>402229</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>789561</t>
+          <t>788748</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>822338</t>
+          <t>822736</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,03%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>32413</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59911</t>
+          <t>58690</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39249</t>
+          <t>38846</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67108</t>
+          <t>67588</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78658</t>
+          <t>78416</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114736</t>
+          <t>116061</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>627176</t>
+          <t>628397</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>653861</t>
+          <t>654674</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>543147</t>
+          <t>542667</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>571006</t>
+          <t>571409</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1182606</t>
+          <t>1181281</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1218684</t>
+          <t>1218926</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29473</t>
+          <t>30654</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57195</t>
+          <t>56155</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60383</t>
+          <t>62036</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95780</t>
+          <t>94351</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97968</t>
+          <t>98409</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141613</t>
+          <t>141620</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>623646</t>
+          <t>624686</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>651368</t>
+          <t>650187</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>613794</t>
+          <t>615223</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>649191</t>
+          <t>647538</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1248802</t>
+          <t>1248795</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1292447</t>
+          <t>1292006</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26264</t>
+          <t>25481</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26900</t>
+          <t>25841</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53277</t>
+          <t>51523</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38886</t>
+          <t>39346</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69338</t>
+          <t>67610</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>588353</t>
+          <t>589136</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>606211</t>
+          <t>606246</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>562922</t>
+          <t>564676</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>589299</t>
+          <t>590358</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1161478</t>
+          <t>1163206</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1191930</t>
+          <t>1191470</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23753</t>
+          <t>24418</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12319</t>
+          <t>12545</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30385</t>
+          <t>29450</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,47 +5134,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>6,58%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>34578</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>24104</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>47601</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>3,94%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>2,75%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>34578</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>24337</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>48230</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>3,94%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>405676</t>
+          <t>405011</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>421009</t>
+          <t>420984</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>417415</t>
+          <t>418350</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>435481</t>
+          <t>435255</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,47 +5247,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>97,2%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>842651</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>829628</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>853125</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>96,06%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>94,57%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>97,25%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>766</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>842651</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>828999</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>852892</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>96,06%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>94,5%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22305</t>
+          <t>23216</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>8815</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24059</t>
+          <t>23916</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18100</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39219</t>
+          <t>41338</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>287481</t>
+          <t>286570</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>303566</t>
+          <t>303783</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>329937</t>
+          <t>330080</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>345138</t>
+          <t>345181</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>624563</t>
+          <t>622444</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>645413</t>
+          <t>645682</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18396</t>
+          <t>17716</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13213</t>
+          <t>13368</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31936</t>
+          <t>33511</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19795</t>
+          <t>19768</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42058</t>
+          <t>42369</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>231455</t>
+          <t>232135</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>245734</t>
+          <t>245685</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>357043</t>
+          <t>355468</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>375766</t>
+          <t>375611</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>596772</t>
+          <t>596461</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>619035</t>
+          <t>619062</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>150737</t>
+          <t>149764</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>203071</t>
+          <t>203598</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>229317</t>
+          <t>230262</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>293884</t>
+          <t>293374</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>398486</t>
+          <t>398827</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>481127</t>
+          <t>481472</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3222686</t>
+          <t>3222159</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3275020</t>
+          <t>3275993</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3263150</t>
+          <t>3263660</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3327717</t>
+          <t>3326772</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6501663</t>
+          <t>6501318</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6584304</t>
+          <t>6583963</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31791</t>
+          <t>31773</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58384</t>
+          <t>58077</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26567</t>
+          <t>27812</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49931</t>
+          <t>51926</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65862</t>
+          <t>65447</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97817</t>
+          <t>97521</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>361079</t>
+          <t>361386</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>387672</t>
+          <t>387690</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>345824</t>
+          <t>343829</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>369188</t>
+          <t>367943</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>717401</t>
+          <t>717697</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>749356</t>
+          <t>749771</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26344</t>
+          <t>27601</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50306</t>
+          <t>51873</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41913</t>
+          <t>42384</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68911</t>
+          <t>69822</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75406</t>
+          <t>77746</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112078</t>
+          <t>115678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>540190</t>
+          <t>538623</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>564152</t>
+          <t>562895</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>494633</t>
+          <t>493722</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>521631</t>
+          <t>521160</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1041962</t>
+          <t>1038362</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1078634</t>
+          <t>1076294</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22760</t>
+          <t>22134</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45852</t>
+          <t>45531</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51521</t>
+          <t>51396</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82386</t>
+          <t>81786</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81030</t>
+          <t>77441</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119527</t>
+          <t>117301</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>623245</t>
+          <t>623566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>646337</t>
+          <t>646963</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>579000</t>
+          <t>579600</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>609865</t>
+          <t>609990</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1210956</t>
+          <t>1213182</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1249453</t>
+          <t>1253042</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,18%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14130</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32773</t>
+          <t>33555</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38209</t>
+          <t>36123</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65312</t>
+          <t>64843</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56040</t>
+          <t>56557</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89811</t>
+          <t>88538</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>613275</t>
+          <t>612493</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>631918</t>
+          <t>632747</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>583765</t>
+          <t>584234</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>610868</t>
+          <t>612954</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1205314</t>
+          <t>1206587</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1239085</t>
+          <t>1238568</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>10975</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29855</t>
+          <t>30230</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28820</t>
+          <t>27663</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54199</t>
+          <t>54241</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44605</t>
+          <t>43153</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76316</t>
+          <t>75920</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>448063</t>
+          <t>447688</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>466497</t>
+          <t>466943</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>442650</t>
+          <t>442608</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>468029</t>
+          <t>469186</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>898451</t>
+          <t>898847</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>930162</t>
+          <t>931614</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10509</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8004</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21799</t>
+          <t>23397</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10873</t>
+          <t>11399</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27786</t>
+          <t>27404</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>323821</t>
+          <t>324069</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332486</t>
+          <t>332519</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>355963</t>
+          <t>354365</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>369758</t>
+          <t>369735</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>684306</t>
+          <t>684688</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>701219</t>
+          <t>700693</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>4044</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14881</t>
+          <t>15076</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>11973</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31768</t>
+          <t>31093</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18814</t>
+          <t>18176</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40684</t>
+          <t>41346</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>242117</t>
+          <t>241922</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>252826</t>
+          <t>252954</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>368401</t>
+          <t>369076</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>387764</t>
+          <t>388196</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>616483</t>
+          <t>615821</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>638353</t>
+          <t>638991</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>142682</t>
+          <t>143896</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>196124</t>
+          <t>193843</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>242891</t>
+          <t>250472</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>311813</t>
+          <t>315818</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>409329</t>
+          <t>408350</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>495829</t>
+          <t>493309</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3198226</t>
+          <t>3200507</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3251668</t>
+          <t>3250454</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3232729</t>
+          <t>3228724</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3301651</t>
+          <t>3294070</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6443063</t>
+          <t>6445583</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6529563</t>
+          <t>6530542</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>65807</t>
+          <t>57110</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44157</t>
+          <t>37477</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98280</t>
+          <t>83051</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>31888</t>
+          <t>38525</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19608</t>
+          <t>24539</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47877</t>
+          <t>57572</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>97694</t>
+          <t>95635</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70809</t>
+          <t>71659</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132568</t>
+          <t>126772</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>334180</t>
+          <t>350683</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>301707</t>
+          <t>324742</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>355830</t>
+          <t>370316</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>278961</t>
+          <t>321316</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>262972</t>
+          <t>302269</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>291241</t>
+          <t>335302</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>613142</t>
+          <t>671999</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>578268</t>
+          <t>640862</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>640027</t>
+          <t>695975</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>310849</t>
+          <t>359841</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>310849</t>
+          <t>359841</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>310849</t>
+          <t>359841</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>710836</t>
+          <t>767634</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>710836</t>
+          <t>767634</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>710836</t>
+          <t>767634</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49379</t>
+          <t>52418</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>37486</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67319</t>
+          <t>70993</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>59807</t>
+          <t>66178</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36696</t>
+          <t>50822</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78295</t>
+          <t>83178</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>109185</t>
+          <t>118596</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81938</t>
+          <t>99050</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>134816</t>
+          <t>144916</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>374168</t>
+          <t>424472</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>356228</t>
+          <t>405897</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>389738</t>
+          <t>439404</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>445864</t>
+          <t>428681</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>427376</t>
+          <t>411681</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>468975</t>
+          <t>444037</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>820033</t>
+          <t>853153</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>794402</t>
+          <t>826833</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>847280</t>
+          <t>872699</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>89,81%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505671</t>
+          <t>494859</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505671</t>
+          <t>494859</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505671</t>
+          <t>494859</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>929218</t>
+          <t>971749</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>929218</t>
+          <t>971749</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>929218</t>
+          <t>971749</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>62807</t>
+          <t>70113</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48989</t>
+          <t>55089</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78562</t>
+          <t>88857</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>61187</t>
+          <t>72374</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50649</t>
+          <t>59858</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73655</t>
+          <t>86360</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>123994</t>
+          <t>142487</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105344</t>
+          <t>121055</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>143352</t>
+          <t>163654</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>473531</t>
+          <t>550724</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>457776</t>
+          <t>531980</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>487349</t>
+          <t>565748</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>479873</t>
+          <t>548304</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>467405</t>
+          <t>534318</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>490411</t>
+          <t>560820</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>953405</t>
+          <t>1099028</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>934047</t>
+          <t>1077861</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>972055</t>
+          <t>1120460</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541060</t>
+          <t>620678</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541060</t>
+          <t>620678</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541060</t>
+          <t>620678</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1077399</t>
+          <t>1241515</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1077399</t>
+          <t>1241515</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1077399</t>
+          <t>1241515</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67517</t>
+          <t>73290</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28107</t>
+          <t>56603</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102144</t>
+          <t>91169</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>100151</t>
+          <t>110358</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82498</t>
+          <t>94978</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117127</t>
+          <t>127961</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>167668</t>
+          <t>183648</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>99724</t>
+          <t>160940</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>206775</t>
+          <t>207136</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>817289</t>
+          <t>624290</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>782662</t>
+          <t>606411</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>856699</t>
+          <t>640977</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>610213</t>
+          <t>623926</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>593237</t>
+          <t>606323</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>627866</t>
+          <t>639306</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1427503</t>
+          <t>1248216</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1388396</t>
+          <t>1224728</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1495447</t>
+          <t>1270924</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>88,76%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>884806</t>
+          <t>697580</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>884806</t>
+          <t>697580</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>884806</t>
+          <t>697580</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>710364</t>
+          <t>734284</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>710364</t>
+          <t>734284</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>710364</t>
+          <t>734284</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1595171</t>
+          <t>1431864</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1595171</t>
+          <t>1431864</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1595171</t>
+          <t>1431864</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>43839</t>
+          <t>49700</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32876</t>
+          <t>37707</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56562</t>
+          <t>63323</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>65200</t>
+          <t>73435</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54630</t>
+          <t>60769</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77185</t>
+          <t>85317</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>109039</t>
+          <t>123135</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93283</t>
+          <t>106336</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>126919</t>
+          <t>142512</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>515440</t>
+          <t>557723</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>502717</t>
+          <t>544100</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>526403</t>
+          <t>569716</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>477335</t>
+          <t>531548</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>465350</t>
+          <t>519666</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>487905</t>
+          <t>544214</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>992775</t>
+          <t>1089271</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>974895</t>
+          <t>1069894</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1008531</t>
+          <t>1106070</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,23%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>559279</t>
+          <t>607423</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>559279</t>
+          <t>607423</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>559279</t>
+          <t>607423</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>542535</t>
+          <t>604983</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>542535</t>
+          <t>604983</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>542535</t>
+          <t>604983</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1101814</t>
+          <t>1212406</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1101814</t>
+          <t>1212406</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1101814</t>
+          <t>1212406</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20477</t>
+          <t>23599</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13856</t>
+          <t>16569</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28431</t>
+          <t>33080</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>39665</t>
+          <t>45310</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16650</t>
+          <t>36720</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63329</t>
+          <t>55721</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>60142</t>
+          <t>68909</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32195</t>
+          <t>56476</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81369</t>
+          <t>81522</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>346970</t>
+          <t>382612</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>339016</t>
+          <t>373131</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>353591</t>
+          <t>389642</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>568158</t>
+          <t>393243</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>544494</t>
+          <t>382832</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>591173</t>
+          <t>401833</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>915128</t>
+          <t>775856</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>893901</t>
+          <t>763243</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>943075</t>
+          <t>788289</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607823</t>
+          <t>438553</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607823</t>
+          <t>438553</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607823</t>
+          <t>438553</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975270</t>
+          <t>844765</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975270</t>
+          <t>844765</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975270</t>
+          <t>844765</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>15189</t>
+          <t>16699</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10231</t>
+          <t>11435</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21367</t>
+          <t>23965</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>35095</t>
+          <t>39002</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27509</t>
+          <t>31105</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44361</t>
+          <t>49052</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>50284</t>
+          <t>55701</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40596</t>
+          <t>45637</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61930</t>
+          <t>67461</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>267570</t>
+          <t>293499</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>261392</t>
+          <t>286233</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>272528</t>
+          <t>298763</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>390435</t>
+          <t>425324</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>381169</t>
+          <t>415274</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>398021</t>
+          <t>433221</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>658005</t>
+          <t>718824</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>646359</t>
+          <t>707064</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>667693</t>
+          <t>728888</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425530</t>
+          <t>464326</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425530</t>
+          <t>464326</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425530</t>
+          <t>464326</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708289</t>
+          <t>774525</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708289</t>
+          <t>774525</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708289</t>
+          <t>774525</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>325015</t>
+          <t>342929</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>255310</t>
+          <t>302109</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>379206</t>
+          <t>386344</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>392992</t>
+          <t>445182</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>320292</t>
+          <t>411567</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>440376</t>
+          <t>484539</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>718007</t>
+          <t>788111</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>623311</t>
+          <t>732522</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>790962</t>
+          <t>840964</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3129149</t>
+          <t>3184004</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3074958</t>
+          <t>3140589</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3198854</t>
+          <t>3224824</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3250840</t>
+          <t>3272343</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3203456</t>
+          <t>3232986</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3323540</t>
+          <t>3305958</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6379989</t>
+          <t>6456347</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6307034</t>
+          <t>6403494</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6474685</t>
+          <t>6511936</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3454164</t>
+          <t>3526933</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3454164</t>
+          <t>3526933</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3454164</t>
+          <t>3526933</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3643832</t>
+          <t>3717525</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3643832</t>
+          <t>3717525</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3643832</t>
+          <t>3717525</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7097996</t>
+          <t>7244458</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7097996</t>
+          <t>7244458</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7097996</t>
+          <t>7244458</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
